--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260828.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>11,100,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>17.19%</t>
+          <t>16.02%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.31%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>5.60%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.24%</t>
         </is>
       </c>
     </row>
@@ -704,183 +704,183 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>5.01%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>1,087,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.88%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>1,087,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>9,785,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>9,785,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,880,000</t>
+          <t>760,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>2,880,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>660,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>621,000</t>
+          <t>650,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -968,139 +968,139 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>179,500</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,900,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>1,050,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>10,378,000</t>
+          <t>149,500</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>936,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1342,51 +1342,51 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1430,51 +1430,51 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>9,293,121,405</t>
+          <t>8,765,278,891</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,128,312,859</t>
+          <t>3,654,126,552</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>5,457,566,030</t>
+          <t>4,808,333,632</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
